--- a/SGC-CKN/Excel/084fafd2-86df-483d-9caf-dee6f8394f92_Cọc_khoan_nhồi_P7-45_D800_01-04-2026.xlsx
+++ b/SGC-CKN/Excel/084fafd2-86df-483d-9caf-dee6f8394f92_Cọc_khoan_nhồi_P7-45_D800_01-04-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="75">
   <si>
     <t>Dự án</t>
   </si>
@@ -59,7 +59,7 @@
     <t>Kết thúc thi công</t>
   </si>
   <si>
-    <t>12:45 01/04/2026</t>
+    <t>12:15 01/04/2026</t>
   </si>
   <si>
     <t>Địa chất TT</t>
@@ -115,6 +115,10 @@
     <t>Cát pha xám ghi, xám nâu TT dẻo</t>
   </si>
   <si>
+    <t xml:space="preserve">22:31
+31/03/2026</t>
+  </si>
+  <si>
     <t xml:space="preserve">23:00
 31/03/2026</t>
   </si>
@@ -145,6 +149,10 @@
     <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
   </si>
   <si>
+    <t xml:space="preserve">02:01
+01/04/2026</t>
+  </si>
+  <si>
     <t xml:space="preserve">02:50
 01/04/2026</t>
   </si>
@@ -155,6 +163,10 @@
     <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt</t>
   </si>
   <si>
+    <t xml:space="preserve">02:51
+01/04/2026</t>
+  </si>
+  <si>
     <t xml:space="preserve">04:00
 01/04/2026</t>
   </si>
@@ -165,41 +177,53 @@
     <t>Sỏi xám vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
+    <t xml:space="preserve">04:01
+01/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05:00
+01/04/2026</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>TK-16.1.Cát xạm, xám vàng, xám xanh, TT rất chặt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06:00
+01/04/2026</t>
+  </si>
+  <si>
     <t xml:space="preserve">06:45
 01/04/2026</t>
   </si>
   <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>TK-16.1.Cát xạm, xám vàng, xám xanh, TT rất chặt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06:00
+    <t>9</t>
+  </si>
+  <si>
+    <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07:05
 01/04/2026</t>
   </si>
   <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09:05
+    <t xml:space="preserve">09:07
 01/04/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">09:40
+    <t>10</t>
+  </si>
+  <si>
+    <t>Cuội đa màu sắc TT rất chặt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09:08
 01/04/2026</t>
   </si>
   <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>Cuội đa màu sắc TT rất chặt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12:45
+    <t xml:space="preserve">12:15
 01/04/2026</t>
   </si>
   <si>
@@ -1221,7 +1245,7 @@
         <v>29</v>
       </c>
       <c r="F11" s="5">
-        <v>-3.26</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5">
         <v>-6.5</v>
@@ -1230,10 +1254,10 @@
         <v>0.5</v>
       </c>
       <c r="I11" s="5">
-        <v>3.24</v>
+        <v>6.5</v>
       </c>
       <c r="J11" s="8">
-        <v>6.48</v>
+        <v>13</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1250,10 +1274,10 @@
         <v>32</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F12" s="9">
         <v>-6.5</v>
@@ -1262,13 +1286,13 @@
         <v>-8.5</v>
       </c>
       <c r="H12" s="9">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="I12" s="9">
         <v>2</v>
       </c>
       <c r="J12" s="12">
-        <v>4</v>
+        <v>4.14</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>30</v>
@@ -1276,34 +1300,34 @@
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B13" s="13" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F13" s="13">
         <v>-8.5</v>
       </c>
       <c r="G13" s="13">
-        <v>-16.8</v>
+        <v>-16.7</v>
       </c>
       <c r="H13" s="13">
         <v>2</v>
       </c>
       <c r="I13" s="13">
-        <v>8.3</v>
+        <v>8.2</v>
       </c>
       <c r="J13" s="12">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="K13" s="14" t="s">
         <v>30</v>
@@ -1311,22 +1335,22 @@
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B14" s="16" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F14" s="16">
-        <v>-16.8</v>
+        <v>-16.7</v>
       </c>
       <c r="G14" s="16">
         <v>-21.1</v>
@@ -1335,10 +1359,10 @@
         <v>1</v>
       </c>
       <c r="I14" s="16">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="J14" s="12">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K14" s="17" t="s">
         <v>30</v>
@@ -1346,19 +1370,19 @@
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B15" s="19" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F15" s="19">
         <v>-21.1</v>
@@ -1367,13 +1391,13 @@
         <v>-24.9</v>
       </c>
       <c r="H15" s="19">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="I15" s="19">
         <v>3.8</v>
       </c>
       <c r="J15" s="12">
-        <v>4.56</v>
+        <v>4.65</v>
       </c>
       <c r="K15" s="20" t="s">
         <v>30</v>
@@ -1381,19 +1405,19 @@
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B16" s="22" t="s">
         <v>11</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E16" s="24" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F16" s="22">
         <v>-24.9</v>
@@ -1402,13 +1426,13 @@
         <v>-34.9</v>
       </c>
       <c r="H16" s="22">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="I16" s="22">
         <v>10</v>
       </c>
       <c r="J16" s="8">
-        <v>8.57</v>
+        <v>8.7</v>
       </c>
       <c r="K16" s="23" t="s">
         <v>30</v>
@@ -1416,34 +1440,34 @@
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B17" s="25" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="26" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E17" s="27" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F17" s="25">
         <v>-34.9</v>
       </c>
       <c r="G17" s="25">
-        <v>-38.4</v>
+        <v>-37.4</v>
       </c>
       <c r="H17" s="25">
-        <v>2.75</v>
+        <v>0.98</v>
       </c>
       <c r="I17" s="25">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="J17" s="12">
-        <v>1.27</v>
+        <v>2.54</v>
       </c>
       <c r="K17" s="26" t="s">
         <v>30</v>
@@ -1451,22 +1475,22 @@
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B18" s="28" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="29" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D18" s="30" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E18" s="30" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="F18" s="28">
-        <v>-38.4</v>
+        <v>-37.4</v>
       </c>
       <c r="G18" s="28">
         <v>-39.5</v>
@@ -1475,10 +1499,10 @@
         <v>0.75</v>
       </c>
       <c r="I18" s="28">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J18" s="12">
-        <v>1.47</v>
+        <v>2.8</v>
       </c>
       <c r="K18" s="29" t="s">
         <v>30</v>
@@ -1486,34 +1510,34 @@
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="31" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B19" s="31" t="s">
         <v>11</v>
       </c>
       <c r="C19" s="32" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D19" s="33" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E19" s="33" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F19" s="31">
         <v>-39.5</v>
       </c>
       <c r="G19" s="31">
-        <v>-43.4</v>
+        <v>-43.7</v>
       </c>
       <c r="H19" s="31">
-        <v>0.58</v>
+        <v>2.03</v>
       </c>
       <c r="I19" s="31">
-        <v>3.9</v>
-      </c>
-      <c r="J19" s="8">
-        <v>6.69</v>
+        <v>4.2</v>
+      </c>
+      <c r="J19" s="12">
+        <v>2.07</v>
       </c>
       <c r="K19" s="32" t="s">
         <v>30</v>
@@ -1521,34 +1545,34 @@
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="34" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B20" s="34" t="s">
         <v>11</v>
       </c>
       <c r="C20" s="35" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D20" s="36" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="E20" s="36" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="F20" s="34">
-        <v>-43.4</v>
+        <v>-43.7</v>
       </c>
       <c r="G20" s="34">
         <v>-44.65</v>
       </c>
       <c r="H20" s="34">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="I20" s="34">
-        <v>1.25</v>
+        <v>0.95</v>
       </c>
       <c r="J20" s="37">
-        <v>0.41</v>
+        <v>0.3</v>
       </c>
       <c r="K20" s="35" t="s">
         <v>30</v>
@@ -1556,7 +1580,7 @@
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="38" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="B23" s="38"/>
       <c r="C23" s="38"/>
@@ -1662,31 +1686,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1703,7 +1727,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>-3.26</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5">
         <v>-6.5</v>
@@ -1712,10 +1736,10 @@
         <v>0.5</v>
       </c>
       <c r="H2" s="5">
-        <v>3.24</v>
+        <v>6.5</v>
       </c>
       <c r="I2" s="8">
-        <v>6.48</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1738,13 +1762,13 @@
         <v>-8.5</v>
       </c>
       <c r="G3" s="9">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="H3" s="9">
         <v>2</v>
       </c>
       <c r="I3" s="12">
-        <v>4</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1755,7 +1779,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D4" s="13">
         <v>1</v>
@@ -1764,16 +1788,16 @@
         <v>-8.5</v>
       </c>
       <c r="F4" s="13">
-        <v>-16.8</v>
+        <v>-16.7</v>
       </c>
       <c r="G4" s="13">
         <v>2</v>
       </c>
       <c r="H4" s="13">
-        <v>8.3</v>
+        <v>8.2</v>
       </c>
       <c r="I4" s="12">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1784,13 +1808,13 @@
         <v>11</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D5" s="16">
         <v>1</v>
       </c>
       <c r="E5" s="16">
-        <v>-16.8</v>
+        <v>-16.7</v>
       </c>
       <c r="F5" s="16">
         <v>-21.1</v>
@@ -1799,10 +1823,10 @@
         <v>1</v>
       </c>
       <c r="H5" s="16">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I5" s="12">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1813,7 +1837,7 @@
         <v>11</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D6" s="19">
         <v>1</v>
@@ -1825,13 +1849,13 @@
         <v>-24.9</v>
       </c>
       <c r="G6" s="19">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="H6" s="19">
         <v>3.8</v>
       </c>
       <c r="I6" s="12">
-        <v>4.56</v>
+        <v>4.65</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1842,7 +1866,7 @@
         <v>11</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D7" s="22">
         <v>1</v>
@@ -1854,13 +1878,13 @@
         <v>-34.9</v>
       </c>
       <c r="G7" s="22">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="H7" s="22">
         <v>10</v>
       </c>
       <c r="I7" s="8">
-        <v>8.57</v>
+        <v>8.7</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1871,7 +1895,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D8" s="25">
         <v>1</v>
@@ -1880,16 +1904,16 @@
         <v>-34.9</v>
       </c>
       <c r="F8" s="25">
-        <v>-38.4</v>
+        <v>-37.4</v>
       </c>
       <c r="G8" s="25">
-        <v>2.75</v>
+        <v>0.98</v>
       </c>
       <c r="H8" s="25">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="I8" s="12">
-        <v>1.27</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1900,13 +1924,13 @@
         <v>11</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D9" s="28">
         <v>1</v>
       </c>
       <c r="E9" s="28">
-        <v>-38.4</v>
+        <v>-37.4</v>
       </c>
       <c r="F9" s="28">
         <v>-39.5</v>
@@ -1915,10 +1939,10 @@
         <v>0.75</v>
       </c>
       <c r="H9" s="28">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="I9" s="12">
-        <v>1.47</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1929,7 +1953,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D10" s="31">
         <v>1</v>
@@ -1938,16 +1962,16 @@
         <v>-39.5</v>
       </c>
       <c r="F10" s="31">
-        <v>-43.4</v>
+        <v>-43.7</v>
       </c>
       <c r="G10" s="31">
-        <v>0.58</v>
+        <v>2.03</v>
       </c>
       <c r="H10" s="31">
-        <v>3.9</v>
-      </c>
-      <c r="I10" s="8">
-        <v>6.69</v>
+        <v>4.2</v>
+      </c>
+      <c r="I10" s="12">
+        <v>2.07</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1958,30 +1982,30 @@
         <v>11</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D11" s="34">
         <v>1</v>
       </c>
       <c r="E11" s="34">
-        <v>-43.4</v>
+        <v>-43.7</v>
       </c>
       <c r="F11" s="34">
         <v>-44.65</v>
       </c>
       <c r="G11" s="34">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="H11" s="34">
-        <v>1.25</v>
+        <v>0.95</v>
       </c>
       <c r="I11" s="37">
-        <v>0.41</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="39" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B12" s="40" t="s">
         <v>30</v>
@@ -1993,19 +2017,19 @@
         <v>10</v>
       </c>
       <c r="E12" s="40">
-        <v>-3.26</v>
+        <v>0</v>
       </c>
       <c r="F12" s="40">
         <v>-44.65</v>
       </c>
       <c r="G12" s="40">
-        <v>13.17</v>
+        <v>12.83</v>
       </c>
       <c r="H12" s="40">
-        <v>41.39</v>
+        <v>44.65</v>
       </c>
       <c r="I12" s="40">
-        <v>3.14</v>
+        <v>3.48</v>
       </c>
     </row>
   </sheetData>
